--- a/raw/1930election.xlsx
+++ b/raw/1930election.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Dropbox/MyData/USvoting/historical voting/1920to1974/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D64D2E4-8C4D-7549-9C0B-5305CDF04E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D688A86B-657F-5141-8AEB-2D3A3D8F8F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="16460" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8420" yWindow="500" windowWidth="16460" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12150,7 +12150,7 @@
         <v>6</v>
       </c>
       <c r="D225">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E225" t="s">
         <v>343</v>
